--- a/wedstrijden_u21.xlsx
+++ b/wedstrijden_u21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbe\Desktop\voorspelling voetbal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6057D51D-AAD7-4295-A5B7-4DA923224800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A7F477-A1D5-4C26-9C7A-E390656B6E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15A2D9A5-3316-4429-AB24-34FCD79D377B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="13">
   <si>
     <t>Datum</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Desselgem</t>
-  </si>
-  <si>
-    <t>Lauwe</t>
   </si>
   <si>
     <t>Beveren-Leie</t>
@@ -484,7 +481,7 @@
         <v>46039</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -501,7 +498,7 @@
         <v>46040</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -518,10 +515,10 @@
         <v>46040</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -535,10 +532,10 @@
         <v>46046</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -555,7 +552,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -586,10 +583,10 @@
         <v>46047</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -603,7 +600,7 @@
         <v>46052</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -637,10 +634,10 @@
         <v>46059</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -654,7 +651,7 @@
         <v>46060</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -674,7 +671,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -688,7 +685,7 @@
         <v>46061</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -708,7 +705,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -722,10 +719,10 @@
         <v>46068</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -739,10 +736,10 @@
         <v>46071</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -756,10 +753,10 @@
         <v>46073</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -773,10 +770,10 @@
         <v>46075</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -790,7 +787,7 @@
         <v>46081</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -807,10 +804,10 @@
         <v>46081</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -827,7 +824,7 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -844,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -858,7 +855,7 @@
         <v>46087</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
@@ -875,7 +872,7 @@
         <v>46087</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -892,7 +889,7 @@
         <v>46088</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -909,7 +906,7 @@
         <v>46096</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
         <v>6</v>
@@ -929,7 +926,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -946,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -960,10 +957,10 @@
         <v>46101</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -994,10 +991,10 @@
         <v>46102</v>
       </c>
       <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
         <v>12</v>
-      </c>
-      <c r="C32" t="s">
-        <v>13</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1011,7 +1008,7 @@
         <v>46103</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -1045,7 +1042,7 @@
         <v>46106</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" t="s">
         <v>6</v>
@@ -1062,10 +1059,10 @@
         <v>46109</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1099,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -1113,10 +1110,10 @@
         <v>46110</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D39">
         <v>5</v>
